--- a/AUTOvalorant/availableAgents.xlsx
+++ b/AUTOvalorant/availableAgents.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\inGameSelection\AUTOvalorant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E79ED6-B2FD-41A6-BF10-36F5E0FC6BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CD793-E802-43CE-BE29-C24670600E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
+    <workbookView xWindow="5265" yWindow="5580" windowWidth="28800" windowHeight="15345" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="36">
   <si>
     <t>Agent</t>
   </si>
@@ -127,14 +127,31 @@
   </si>
   <si>
     <t>clove</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>1 initator,  2 dualist, 3 sentinel, 4 controller</t>
+  </si>
+  <si>
+    <t>vyse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -168,9 +185,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,13 +503,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
+    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -499,33 +518,36 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -542,16 +564,22 @@
       <c r="H2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -568,16 +596,19 @@
       <c r="H3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -594,16 +625,19 @@
       <c r="H4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -620,16 +654,19 @@
       <c r="H5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -646,16 +683,19 @@
       <c r="H6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>28</v>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -663,22 +703,25 @@
       <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
+      <c r="F7" t="s">
         <v>28</v>
       </c>
       <c r="H7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
+      <c r="C8">
+        <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -686,33 +729,42 @@
       <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
-        <v>28</v>
+      <c r="C9">
+        <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>28</v>
+      <c r="C10">
+        <v>4</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -720,16 +772,19 @@
       <c r="E10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
+      <c r="C11">
+        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -737,19 +792,22 @@
       <c r="E11" t="s">
         <v>28</v>
       </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
-        <v>28</v>
+      <c r="C12">
+        <v>2</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -757,19 +815,22 @@
       <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
-        <v>28</v>
+      <c r="C13">
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -777,16 +838,19 @@
       <c r="E13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
+      <c r="C14">
+        <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -794,16 +858,19 @@
       <c r="E14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
-        <v>28</v>
+      <c r="C15">
+        <v>2</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
@@ -820,16 +887,19 @@
       <c r="H15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
+      <c r="C16">
+        <v>4</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -837,16 +907,19 @@
       <c r="E16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
-      <c r="C17" t="s">
-        <v>28</v>
+      <c r="C17">
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -863,16 +936,19 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" t="s">
-        <v>28</v>
+      <c r="C18">
+        <v>4</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -886,16 +962,19 @@
       <c r="G18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
-        <v>28</v>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -903,16 +982,19 @@
       <c r="E19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
-        <v>28</v>
+      <c r="C20">
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -920,16 +1002,19 @@
       <c r="E20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>28</v>
+      <c r="C21">
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -937,19 +1022,22 @@
       <c r="E21" t="s">
         <v>28</v>
       </c>
-      <c r="H21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
-      <c r="C22" t="s">
-        <v>28</v>
+      <c r="C22">
+        <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -957,19 +1045,22 @@
       <c r="E22" t="s">
         <v>28</v>
       </c>
-      <c r="H22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
-        <v>28</v>
+      <c r="C23">
+        <v>3</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
@@ -977,16 +1068,19 @@
       <c r="E23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="C24" t="s">
-        <v>28</v>
+      <c r="C24">
+        <v>2</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
@@ -1003,18 +1097,41 @@
       <c r="H24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H24">
+  <autoFilter ref="A1:I1" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I25">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/AUTOvalorant/availableAgents.xlsx
+++ b/AUTOvalorant/availableAgents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\inGameSelection\AUTOvalorant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CD793-E802-43CE-BE29-C24670600E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC499C9-63A7-4281-86F4-8383F576F5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="5580" windowWidth="28800" windowHeight="15345" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -547,7 +547,7 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -573,13 +573,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -590,25 +590,19 @@
       <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
       <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -617,27 +611,18 @@
         <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -660,13 +645,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -675,27 +660,18 @@
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -704,9 +680,6 @@
         <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" t="s">
         <v>28</v>
       </c>
       <c r="I7" t="s">
@@ -715,13 +688,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -732,19 +705,25 @@
       <c r="F8" t="s">
         <v>28</v>
       </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -753,18 +732,27 @@
         <v>28</v>
       </c>
       <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -773,15 +761,18 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -801,13 +792,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -818,19 +809,25 @@
       <c r="F12" t="s">
         <v>28</v>
       </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
       <c r="H12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -844,10 +841,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -861,13 +858,22 @@
       <c r="F14" t="s">
         <v>28</v>
       </c>
+      <c r="G14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -893,13 +899,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -908,18 +914,27 @@
         <v>28</v>
       </c>
       <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -928,27 +943,18 @@
         <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -957,21 +963,15 @@
         <v>28</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -988,33 +988,27 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -1023,6 +1017,9 @@
         <v>28</v>
       </c>
       <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
         <v>28</v>
       </c>
       <c r="I21" t="s">
@@ -1031,13 +1028,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
       <c r="C22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -1046,18 +1043,15 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1074,14 +1068,14 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
         <v>3</v>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
       <c r="D24" t="s">
         <v>28</v>
       </c>
@@ -1095,32 +1089,38 @@
         <v>28</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1131,8 +1131,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I25">
-      <sortCondition ref="A1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
+      <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AUTOvalorant/availableAgents.xlsx
+++ b/AUTOvalorant/availableAgents.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\inGameSelection\AUTOvalorant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC499C9-63A7-4281-86F4-8383F576F5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F643122-9695-4029-B83B-1BE7B19E7605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
+    <workbookView xWindow="21840" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$J$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="39">
   <si>
     <t>Agent</t>
   </si>
@@ -136,6 +136,15 @@
   </si>
   <si>
     <t>vyse</t>
+  </si>
+  <si>
+    <t>Tin Synix</t>
+  </si>
+  <si>
+    <t>account</t>
+  </si>
+  <si>
+    <t>update</t>
   </si>
 </sst>
 </file>
@@ -185,10 +194,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,14 +513,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -538,13 +549,22 @@
       <c r="I1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -558,221 +578,287 @@
       <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
       <c r="H2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>45548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3" s="3">
+        <v>45547</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="O5" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6" s="3">
+        <v>45555</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
+        <v>45617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
       <c r="H10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -786,19 +872,28 @@
       <c r="F11" t="s">
         <v>28</v>
       </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
       <c r="H11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -809,25 +904,16 @@
       <c r="F12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -838,42 +924,42 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14">
         <v>3</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
       <c r="H14" t="s">
         <v>28</v>
       </c>
-      <c r="I14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -887,25 +973,16 @@
       <c r="F15" t="s">
         <v>28</v>
       </c>
-      <c r="G15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -914,27 +991,18 @@
         <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -948,13 +1016,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -968,13 +1036,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -983,32 +1051,56 @@
         <v>28</v>
       </c>
       <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -1017,24 +1109,18 @@
         <v>28</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -1048,10 +1134,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1065,16 +1151,22 @@
       <c r="F23" t="s">
         <v>28</v>
       </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
@@ -1083,9 +1175,6 @@
         <v>28</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" t="s">
         <v>28</v>
       </c>
       <c r="H24" t="s">
@@ -1094,13 +1183,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
         <v>28</v>
@@ -1109,18 +1198,15 @@
         <v>28</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1128,11 +1214,62 @@
       <c r="D26" t="s">
         <v>28</v>
       </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
-      <sortCondition ref="C1"/>
+  <autoFilter ref="A1:J35" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J35">
+      <sortCondition ref="J1:J35"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AUTOvalorant/availableAgents.xlsx
+++ b/AUTOvalorant/availableAgents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\inGameSelection\AUTOvalorant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F643122-9695-4029-B83B-1BE7B19E7605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C439D119-E3D9-466D-94A1-3EA584300604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21840" yWindow="-103" windowWidth="33120" windowHeight="18720" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
+    <workbookView xWindow="24394" yWindow="1894" windowWidth="28852" windowHeight="15369" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -561,13 +561,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -578,7 +578,13 @@
       <c r="F2" t="s">
         <v>28</v>
       </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
       <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
         <v>28</v>
       </c>
       <c r="J2" t="s">
@@ -593,30 +599,21 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="D3" t="s">
         <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
       <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
         <v>28</v>
       </c>
       <c r="J3" t="s">
@@ -887,13 +884,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
         <v>28</v>
@@ -902,15 +899,27 @@
         <v>28</v>
       </c>
       <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -924,22 +933,16 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -947,22 +950,22 @@
       <c r="E14" t="s">
         <v>28</v>
       </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
       <c r="H14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
@@ -971,18 +974,24 @@
         <v>28</v>
       </c>
       <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -996,10 +1005,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1016,13 +1025,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -1036,14 +1045,14 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19">
         <v>3</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
       <c r="D19" t="s">
         <v>28</v>
       </c>
@@ -1051,27 +1060,18 @@
         <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
